--- a/output/pdf_financials_xlsx/PNG.xlsx
+++ b/output/pdf_financials_xlsx/PNG.xlsx
@@ -3120,13 +3120,13 @@
         <v>0.03104</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.03104</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.03104</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.03104</v>
       </c>
     </row>
     <row r="93">
@@ -4700,7 +4700,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PNG.xlsx
+++ b/output/pdf_financials_xlsx/PNG.xlsx
@@ -735,19 +735,19 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000127</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.001048</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.001063</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000496</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.000455</v>
       </c>
     </row>
     <row r="13">
@@ -1197,19 +1197,19 @@
         <v>-0.076388</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.06526999999999999</v>
+        <v>-0.065397</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.049563</v>
+        <v>-0.050611</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.048024</v>
+        <v>-0.049087</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.056205</v>
+        <v>-0.056701</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.031001</v>
+        <v>-0.031456</v>
       </c>
     </row>
     <row r="28">
@@ -1253,19 +1253,19 @@
         <v>-0.076388</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.06526999999999999</v>
+        <v>-0.065397</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.049563</v>
+        <v>-0.050611</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.048024</v>
+        <v>-0.049087</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.056205</v>
+        <v>-0.056701</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.031001</v>
+        <v>-0.031456</v>
       </c>
     </row>
     <row r="30">
@@ -1406,13 +1406,13 @@
         <v>0.248357</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.183875</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.121878</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.096941</v>
       </c>
     </row>
     <row r="35">
@@ -1462,13 +1462,13 @@
         <v>0.248357</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.183875</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.121878</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.096941</v>
       </c>
     </row>
     <row r="37">
@@ -1798,13 +1798,13 @@
         <v>0.000556</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.18899</v>
+        <v>0.005115</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.121878</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.097466</v>
+        <v>0.000525</v>
       </c>
     </row>
     <row r="49">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">

--- a/output/pdf_financials_xlsx/PNG.xlsx
+++ b/output/pdf_financials_xlsx/PNG.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.016116</v>
+        <v>0.016315</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0.016844</v>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.029806</v>
+        <v>0.030005</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0.076388</v>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.029806</v>
+        <v>-0.030005</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-0.076388</v>
@@ -2291,10 +2291,10 @@
         <v>0</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.000278</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.007167</v>
       </c>
     </row>
     <row r="65">
@@ -2366,19 +2366,19 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.0215</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.0065</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.0065</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.0062</v>
       </c>
     </row>
     <row r="68">
@@ -3353,22 +3353,22 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001227</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002298</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.004171</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>0.003893</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-0.004559</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>0.005001</v>
       </c>
       <c r="H101" s="3" t="n">
         <v>0</v>
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.010404</v>
+        <v>-0.011631</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>-0.0496</v>
@@ -3505,10 +3505,10 @@
         <v>-0.045106</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.011899</v>
+        <v>-0.016458</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-0.030907</v>
+        <v>-0.025906</v>
       </c>
       <c r="H106" s="3" t="n">
         <v>0.006589</v>
@@ -6010,7 +6010,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -6461,7 +6465,11 @@
           <t>HST recoverable</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -6828,7 +6836,11 @@
           <t>Write-off of GST recoverable</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -7128,7 +7140,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -7599,7 +7615,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E64" s="5" t="n">
         <v>-0.001227</v>
       </c>
@@ -9660,7 +9680,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E105" s="5" t="n">
         <v>0.000199</v>
       </c>
